--- a/raw_data/tableMaster.xlsx
+++ b/raw_data/tableMaster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhqu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhqu\OneDrive\Documents\JobProjection\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47B4386-546F-48A9-A60F-348A775DDA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A460354-861E-4519-9671-77C25000E803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0B945E46-D09C-4793-AFE9-C8D9EC28E047}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>Median earnings per degree</t>
+  </si>
+  <si>
+    <t>Everything</t>
+  </si>
+  <si>
+    <t>Dashboard/data viz</t>
+  </si>
+  <si>
+    <t>There are misisng data</t>
   </si>
 </sst>
 </file>
@@ -175,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -189,9 +198,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +542,7 @@
     <col min="4" max="4" width="14.6328125" customWidth="1"/>
     <col min="5" max="5" width="18.54296875" customWidth="1"/>
     <col min="6" max="6" width="22.1796875" customWidth="1"/>
-    <col min="7" max="7" width="27.1796875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="27.1796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -569,6 +575,18 @@
       <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
@@ -577,6 +595,18 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
@@ -585,6 +615,18 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
@@ -593,6 +635,18 @@
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
@@ -609,7 +663,7 @@
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -617,7 +671,7 @@
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D8">
@@ -628,7 +682,7 @@
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
     </row>

--- a/raw_data/tableMaster.xlsx
+++ b/raw_data/tableMaster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhqu\OneDrive\Documents\JobProjection\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A460354-861E-4519-9671-77C25000E803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B070C451-C06E-4484-985D-F524C05959FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0B945E46-D09C-4793-AFE9-C8D9EC28E047}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Sheet Name</t>
   </si>
@@ -50,82 +50,55 @@
     <t>What does it contain?</t>
   </si>
   <si>
-    <t>Num of rows</t>
-  </si>
-  <si>
     <t>Possible relations</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>collegeAssoEmplPopRatio25</t>
-  </si>
-  <si>
-    <t>collegeAssoUnemployRate25</t>
-  </si>
-  <si>
-    <t>bachHigherEmplPopRatio25</t>
-  </si>
-  <si>
-    <t>bachHigherUnemployRate25</t>
-  </si>
-  <si>
     <t>employPerDeg</t>
   </si>
   <si>
-    <t>bachelors</t>
-  </si>
-  <si>
     <t>bachelors_and_higher</t>
   </si>
   <si>
     <t>graddeg</t>
   </si>
   <si>
-    <t>medEarnPerField</t>
-  </si>
-  <si>
-    <t>The employment-to-population ratio for college or associate degrees, 25 years or higher</t>
-  </si>
-  <si>
-    <t>The unemployment rate for college or associate degrees, 25 years or higher</t>
-  </si>
-  <si>
     <t>How this will be used</t>
   </si>
   <si>
-    <t>The unemployment rate for bachelor degrees, 25 years or higher</t>
-  </si>
-  <si>
-    <t>The employment-to-population ratio for bachelor degrees, 25 years or higher</t>
-  </si>
-  <si>
     <t>Employment, wages, and projected change in employment by typical entry-level education (Employment in thousands)</t>
   </si>
   <si>
-    <t>Occupation by Field of Bachelor's Degree (2019)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Civilian employed aged 25 to 64 with a bachelor's degree level of education					</t>
-  </si>
-  <si>
     <t>Occupation by Field of Bachelor's Degree or Higher (2019)</t>
   </si>
   <si>
     <t>Occupation by Field of Higher Degree (2019)</t>
   </si>
   <si>
-    <t>Median earnings per degree</t>
-  </si>
-  <si>
-    <t>Everything</t>
-  </si>
-  <si>
-    <t>Dashboard/data viz</t>
-  </si>
-  <si>
-    <t>There are misisng data</t>
+    <t>Typical education needed for entry/Employment, 2024/Employment, 2034/Employment change, numeric, 2024–34/Employment change, percent, 2024–34/Median annual wage, dollars, 2024</t>
+  </si>
+  <si>
+    <t>May use as backup data for data viz or other tables</t>
+  </si>
+  <si>
+    <t>All main cols and get rid of MOE sub cols, get rid of all footnote</t>
+  </si>
+  <si>
+    <t>Most-Recent-Cohorts-Field-of-Study</t>
+  </si>
+  <si>
+    <t>Everything pertains to the field of study: salary, etc.</t>
+  </si>
+  <si>
+    <t>CIPCODE(major code-may keep-match with other tables), CIPDESC(major name), CREDDESC(degree level), EARN_MDN_1YR, EARN_MDN_4YR, EARN_MDN_5YR, EARN_MDN_HI_1YR(highest credential), EARN_MDN_HI_2YR(highest credential), EARN_MDN_4YR_NAT(national median), EARN_P25_4YR_NAT(national median), EARN_P75_4YR_NAT</t>
+  </si>
+  <si>
+    <t>One of main table</t>
+  </si>
+  <si>
+    <t>ONET</t>
   </si>
 </sst>
 </file>
@@ -533,165 +506,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6422DE2-08FA-4CE4-A9E8-5EAD7C1FAB89}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" customWidth="1"/>
-    <col min="7" max="7" width="27.1796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="27.1796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>5</v>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/raw_data/tableMaster.xlsx
+++ b/raw_data/tableMaster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhqu\OneDrive\Documents\JobProjection\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B070C451-C06E-4484-985D-F524C05959FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701FAE52-B49E-48ED-A9F7-A3056E76B7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0B945E46-D09C-4793-AFE9-C8D9EC28E047}"/>
   </bookViews>
@@ -92,13 +92,13 @@
     <t>Everything pertains to the field of study: salary, etc.</t>
   </si>
   <si>
-    <t>CIPCODE(major code-may keep-match with other tables), CIPDESC(major name), CREDDESC(degree level), EARN_MDN_1YR, EARN_MDN_4YR, EARN_MDN_5YR, EARN_MDN_HI_1YR(highest credential), EARN_MDN_HI_2YR(highest credential), EARN_MDN_4YR_NAT(national median), EARN_P25_4YR_NAT(national median), EARN_P75_4YR_NAT</t>
-  </si>
-  <si>
     <t>One of main table</t>
   </si>
   <si>
     <t>ONET</t>
+  </si>
+  <si>
+    <t>CIPDESC(major name), CREDDESC(degree level), EARN_MDN_1YR, EARN_MDN_4YR, EARN_MDN_5YR, EARN_MDN_HI_1YR(highest credential), EARN_MDN_HI_2YR(highest credential), EARN_MDN_4YR_NAT(national median), EARN_P25_4YR_NAT(national median), EARN_P75_4YR_NAT</t>
   </si>
 </sst>
 </file>
@@ -573,7 +573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -581,15 +581,15 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
         <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/raw_data/tableMaster.xlsx
+++ b/raw_data/tableMaster.xlsx
@@ -1,125 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhqu\OneDrive\Documents\JobProjection\raw_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701FAE52-B49E-48ED-A9F7-A3056E76B7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0B945E46-D09C-4793-AFE9-C8D9EC28E047}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Sheet Name</t>
   </si>
   <si>
+    <t>What does it contain?</t>
+  </si>
+  <si>
     <t>Columns to keep</t>
   </si>
   <si>
-    <t>What does it contain?</t>
-  </si>
-  <si>
     <t>Possible relations</t>
   </si>
   <si>
+    <t>How this will be used</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
     <t>employPerDeg</t>
   </si>
   <si>
+    <t>Employment, wages, and projected change in employment by typical entry-level education (Employment in thousands)</t>
+  </si>
+  <si>
+    <t>Typical education needed for entry/Employment, 2024/Employment, 2034/Employment change, numeric, 2024–34/Employment change, percent, 2024–34/Median annual wage, dollars, 2024</t>
+  </si>
+  <si>
+    <t>May use as backup data for data viz or other tables</t>
+  </si>
+  <si>
     <t>bachelors_and_higher</t>
   </si>
   <si>
+    <t>Occupation by Field of Bachelor's Degree or Higher (2019)</t>
+  </si>
+  <si>
+    <t>All main cols and get rid of MOE sub cols, get rid of all footnote</t>
+  </si>
+  <si>
     <t>graddeg</t>
   </si>
   <si>
-    <t>How this will be used</t>
-  </si>
-  <si>
-    <t>Employment, wages, and projected change in employment by typical entry-level education (Employment in thousands)</t>
-  </si>
-  <si>
-    <t>Occupation by Field of Bachelor's Degree or Higher (2019)</t>
-  </si>
-  <si>
     <t>Occupation by Field of Higher Degree (2019)</t>
   </si>
   <si>
-    <t>Typical education needed for entry/Employment, 2024/Employment, 2034/Employment change, numeric, 2024–34/Employment change, percent, 2024–34/Median annual wage, dollars, 2024</t>
-  </si>
-  <si>
-    <t>May use as backup data for data viz or other tables</t>
-  </si>
-  <si>
-    <t>All main cols and get rid of MOE sub cols, get rid of all footnote</t>
-  </si>
-  <si>
     <t>Most-Recent-Cohorts-Field-of-Study</t>
   </si>
   <si>
     <t>Everything pertains to the field of study: salary, etc.</t>
   </si>
   <si>
+    <t>CIPDESC(major name), CREDDESC(degree level), EARN_MDN_1YR, EARN_MDN_4YR, EARN_MDN_5YR, EARN_MDN_HI_1YR(highest credential), EARN_MDN_HI_2YR(highest credential), EARN_MDN_4YR_NAT(national median), EARN_P25_4YR_NAT(national median), EARN_P75_4YR_NAT</t>
+  </si>
+  <si>
     <t>One of main table</t>
-  </si>
-  <si>
-    <t>ONET</t>
-  </si>
-  <si>
-    <t>CIPDESC(major name), CREDDESC(degree level), EARN_MDN_1YR, EARN_MDN_4YR, EARN_MDN_5YR, EARN_MDN_HI_1YR(highest credential), EARN_MDN_HI_2YR(highest credential), EARN_MDN_4YR_NAT(national median), EARN_P25_4YR_NAT(national median), EARN_P75_4YR_NAT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="2">
@@ -140,16 +110,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -159,18 +129,18 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -200,44 +170,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -265,31 +235,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -317,23 +270,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -345,136 +281,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -496,103 +476,98 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6422DE2-08FA-4CE4-A9E8-5EAD7C1FAB89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="3" width="32.453125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="5" max="5" width="22.1796875" customWidth="1"/>
-    <col min="6" max="6" width="27.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="30.571428571428573" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="32.42857142857143" customWidth="1"/>
+    <col min="4" max="4" width="18.571428571428573" customWidth="1"/>
+    <col min="5" max="5" width="22.142857142857142" customWidth="1"/>
+    <col min="6" max="6" width="27.142857142857142" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="87" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="3" ht="29.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="4" ht="29.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
+    <row r="5" ht="159.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>18</v>
-      </c>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>